--- a/parameter_distributions.xlsx
+++ b/parameter_distributions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shxin\OneDrive - UTS\桌面\Bio\microalgae\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2497F5DA-4624-4D51-97FC-3BD405D2E06D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B0C1273-0472-4586-A972-146C0484305A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13200" yWindow="32280" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9686" yWindow="3523" windowWidth="21600" windowHeight="11100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
